--- a/liste prix ventes articles part5.xlsx
+++ b/liste prix ventes articles part5.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:C210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3553,6 +3553,21 @@
         <v>250</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>YAO00075</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>YAOURT DOLAIT OLE FLACON 500ML</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
